--- a/data/trans_orig/IQ2605_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ2605_R2-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>83260</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>75909</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89592</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>78,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>71,65%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>84,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>68325</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>61410</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>74514</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>60951</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>74454</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>75,7%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,55%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>83260</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>76158</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>90073</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>78,59%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141821</t>
+          <t>141356</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161082</t>
+          <t>160276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22688</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16356</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30039</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>21,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>28,35%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21936</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15747</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28851</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15807</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29310</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>24,3%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22688</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15875</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>29790</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35126</t>
+          <t>35932</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54387</t>
+          <t>54852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>105948</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>105948</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>105948</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90261</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90261</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90261</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>105948</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>105948</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>105948</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>134273</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>122091</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>146547</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>52,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>48,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>149920</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>137202</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>162160</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>137159</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>162268</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>59,31%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>54,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>64,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>134273</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>120540</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>147327</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>266556</t>
+          <t>264433</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>302371</t>
+          <t>300317</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>119483</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>107209</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>131665</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>47,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>51,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>102837</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90597</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>115555</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>90489</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>115598</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>40,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>35,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>119483</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>106429</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>133216</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>204143</t>
+          <t>206197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>239958</t>
+          <t>242081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252757</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252757</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252757</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71332</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>61407</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81171</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,41%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>57,36%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>60152</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>51165</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>68843</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>50881</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>69060</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>47,16%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>71332</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>61692</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>81824</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,41%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117757</t>
+          <t>117122</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144474</t>
+          <t>143986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70183</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60344</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>80108</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,59%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>42,64%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67396</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58705</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>76383</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58488</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>76667</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>52,84%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>59,89%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70183</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>59691</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>79823</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>49,59%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>124589</t>
+          <t>125077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151306</t>
+          <t>151941</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>84538</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>74638</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>95832</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>36,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>80182</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>69435</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>90770</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>69564</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>91538</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>41,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>35,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>84538</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>73686</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>96092</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>41,16%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>148763</t>
+          <t>150429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180025</t>
+          <t>180375</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>120869</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>109575</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130769</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>58,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>63,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>113915</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>103327</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>124662</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>102559</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>124533</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>58,69%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>64,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>120869</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>109315</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>131721</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>58,84%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219479</t>
+          <t>219129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250741</t>
+          <t>249075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,35%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205407</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205407</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205407</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205407</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205407</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205407</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>373402</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>351905</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>393254</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,65%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>358579</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>336981</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>378576</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>339361</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>379085</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>53,95%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>50,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,96%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>373402</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>350621</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>394190</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>702468</t>
+          <t>702365</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>762083</t>
+          <t>760534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>333224</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>313372</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>354721</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,35%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>454</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>306084</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>286087</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>327682</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>285578</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>325302</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>46,05%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,04%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>49,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>333224</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>312436</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>356005</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>47,16%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>609205</t>
+          <t>610754</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>668820</t>
+          <t>668923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>706626</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>706626</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>706626</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>706626</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>706626</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>706626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>106340</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100524</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>111246</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>90,17%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>85,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>107029</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>99348</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>112446</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>99697</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>113063</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>85,48%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>79,35%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,81%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>106340</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>99861</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>111021</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203529</t>
+          <t>203826</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221017</t>
+          <t>221121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11594</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6688</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17410</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,76%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18181</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12764</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25862</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12147</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25513</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>14,52%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11594</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6913</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>18073</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22127</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39615</t>
+          <t>39318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>117934</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>117934</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>117934</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>125210</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>125210</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>125210</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>117934</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>117934</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>117934</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>208930</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>196929</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>220174</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>77,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>73,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>180874</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>169174</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>190555</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>169859</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>191444</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>76,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>71,61%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>80,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>208930</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>197171</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>219125</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>371709</t>
+          <t>373185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>404892</t>
+          <t>404952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,26%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59381</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>48137</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>26,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>55376</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>45695</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>67076</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>44806</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>66391</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>23,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>59381</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>49186</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>71140</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99669</t>
+          <t>99609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132852</t>
+          <t>131376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268311</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268311</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268311</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268311</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268311</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>100824</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>90542</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>111204</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,58%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>115769</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>106088</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>124049</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>104805</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>124370</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>74,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>68,08%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>100824</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>90768</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>111171</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>63,58%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202119</t>
+          <t>203069</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>230091</t>
+          <t>231234</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>57747</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47367</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>68029</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,87%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>40070</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31790</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49751</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>31469</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>51034</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>25,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>20,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>31,92%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>57747</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>47400</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>67803</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,42%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84319</t>
+          <t>83176</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112291</t>
+          <t>111341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>114665</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>103630</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>126163</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>63,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>57,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,11%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>102632</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>91714</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>112468</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>91187</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>112907</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>60,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>53,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>65,94%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>114665</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>102841</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>124719</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>63,72%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>202892</t>
+          <t>202724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>231585</t>
+          <t>230765</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65290</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>53792</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>76325</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>36,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,89%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>42,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>67937</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>58101</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>78855</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>57662</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>79382</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>39,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>34,06%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>46,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>65290</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>55236</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>77114</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>118939</t>
+          <t>119759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147632</t>
+          <t>147800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170569</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170569</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170569</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>530759</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>511646</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>548841</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>73,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>70,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>506305</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>486435</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>527029</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>485730</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>525483</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>70,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>758</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>530759</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>511119</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>550397</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>73,23%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1007259</t>
+          <t>1006721</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1064264</t>
+          <t>1064836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>194012</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>175930</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>213125</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>26,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>181563</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>160839</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>201433</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>162385</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>202138</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>26,4%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>194012</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>174374</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>213652</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>348375</t>
+          <t>347803</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>405380</t>
+          <t>405918</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>724771</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>724771</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>724771</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>990</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>687868</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>687868</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>687868</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>724771</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>724771</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>724771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>94185</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>86864</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>100545</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>90794</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>82069</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>97745</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>83184</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>97362</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>75,15%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>67,93%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>80,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>94185</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>87093</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>100528</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>80,74%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174692</t>
+          <t>173885</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195129</t>
+          <t>194012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22466</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16106</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29787</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30029</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23078</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>38754</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23461</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>37639</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>24,85%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32,07%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22466</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16123</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>29558</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42345</t>
+          <t>43462</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62782</t>
+          <t>63589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>116651</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>120823</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>116651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>217452</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>205872</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>226375</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>84,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>177289</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>167332</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>184977</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>167855</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>185213</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>84,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>79,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>87,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>217452</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>207345</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>226677</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>84,26%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>380376</t>
+          <t>380589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>406989</t>
+          <t>406900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40609</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31686</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52189</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>33228</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25540</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>43185</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>25304</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42662</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>15,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>20,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40609</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>31384</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50716</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61589</t>
+          <t>61678</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88202</t>
+          <t>87989</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>147479</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>137815</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>156971</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>73,08%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>83,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>141693</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>132019</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>151634</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>130608</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>149995</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>75,21%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,07%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>147479</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>137570</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>156187</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>78,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>275233</t>
+          <t>274815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>303178</t>
+          <t>302818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41093</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>31601</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50757</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>26,92%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>46713</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36772</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>56387</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>38411</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>57798</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>24,79%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,93%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>41093</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>32385</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>51002</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73800</t>
+          <t>74160</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>101745</t>
+          <t>102163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188406</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188406</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188406</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>124660</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>114325</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>133716</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>71,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65,69%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>76,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>116316</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>105418</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>125956</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>105053</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>126260</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,49%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>124660</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>113071</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>134526</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>71,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226690</t>
+          <t>225823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254778</t>
+          <t>255417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,74%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49388</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40332</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59723</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>28,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>23,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>56028</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>46388</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>66926</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>46084</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>67291</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,51%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>49388</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>39522</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>60977</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>28,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>91613</t>
+          <t>90974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119701</t>
+          <t>120568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172344</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172344</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172344</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>583776</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>563535</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>600903</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>79,17%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>76,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>81,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>800</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>526091</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>507772</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>543676</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>507027</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>543833</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>76,01%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,37%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>78,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>562734</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>600860</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>79,17%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1082965</t>
+          <t>1082220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1135614</t>
+          <t>1134290</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,35%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>153556</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136429</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>173797</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>20,83%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>23,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>165998</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>148413</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>184317</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>148256</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>185062</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23,99%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,63%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>153556</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136472</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>174598</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>293807</t>
+          <t>295131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346456</t>
+          <t>347201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1041</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>692089</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>692089</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>692089</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,74 +6564,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10131</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7912</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>90,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>70,85%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12873</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10825</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>78,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11985</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10045</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12729</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>78,92%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12427</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8743</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14310</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>86,84%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>61,1%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25300</t>
+          <t>22116</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27271</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>744</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>484</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11166</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13752</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14310</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>23895</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>34378</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30051</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>37353</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>87,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>76,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29222</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25212</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>31779</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>85,1%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>73,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>92,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39084</t>
+          <t>26060</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35099</t>
+          <t>23006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42020</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>68307</t>
+          <t>60438</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>55392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72225</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2126</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9428</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>23,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2561</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9128</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>9639</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39479</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>34340</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44763</t>
+          <t>30598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79104</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37570</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30965</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43512</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>70,5%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>58,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>81,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28710</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>23385</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33783</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>58,45%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>84,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39037</t>
+          <t>27449</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31789</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>31525</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>67748</t>
+          <t>65019</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58305</t>
+          <t>57183</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75290</t>
+          <t>72996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>79,56%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15723</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9781</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22328</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>29,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>11297</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6224</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>16622</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>15,56%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>28176</t>
+          <t>26730</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20634</t>
+          <t>18753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37619</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>53293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40007</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>38455</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>95924</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54088</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>45481</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>60240</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>72,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>61,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32099</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>25719</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38126</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>58,37%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>46,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55898</t>
+          <t>33902</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47271</t>
+          <t>27241</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62450</t>
+          <t>40293</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87997</t>
+          <t>87991</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77650</t>
+          <t>77568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97697</t>
+          <t>97940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20338</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14186</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28945</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>27,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>22895</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>16868</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29275</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>41,63%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>53,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>23850</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29508</t>
+          <t>30511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>43776</t>
+          <t>44188</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34076</t>
+          <t>34239</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54123</t>
+          <t>54611</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>54994</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>54994</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>54994</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57752</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57752</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76779</t>
+          <t>57752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131773</t>
+          <t>132179</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131773</t>
+          <t>132179</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131773</t>
+          <t>132179</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>136167</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>126085</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>145254</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>70,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>81,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>102905</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>93844</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>111272</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>99396</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134765</t>
+          <t>89886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>157301</t>
+          <t>107975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>249353</t>
+          <t>235563</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236071</t>
+          <t>221415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>263118</t>
+          <t>248795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>42198</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>33111</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>52280</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>18,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>40188</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>31821</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>49249</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>34,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45322</t>
+          <t>40138</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34469</t>
+          <t>31559</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>49648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>85510</t>
+          <t>82336</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71745</t>
+          <t>69104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98792</t>
+          <t>96484</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
